--- a/MST-66_bodywt.xlsx
+++ b/MST-66_bodywt.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Intmed_Shared\Shared\gi\Restricted\higgins_lab\Mouse_exp\MST-66_finerenone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peterhiggins/Documents/RCode/finerenone_mst66/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B41B0A45-BF0E-45AD-B0E0-F8E7E1B0DD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28738992-D187-BB41-A791-FF45E5BE5493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{EE0FFB1A-D207-467A-B10D-FA7B02B99E2E}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="21600" windowHeight="13020" xr2:uid="{EE0FFB1A-D207-467A-B10D-FA7B02B99E2E}"/>
   </bookViews>
   <sheets>
     <sheet name="BW" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="AY">#REF!</definedName>
     <definedName name="Calendar">#REF!</definedName>
@@ -115,7 +112,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -252,11 +249,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -282,6 +299,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -297,34 +317,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="pilot_budget"/>
-      <sheetName val="BW"/>
-      <sheetName val="dosing"/>
-      <sheetName val="exp_compare"/>
-      <sheetName val="sac"/>
-      <sheetName val="genes"/>
-      <sheetName val="RNA"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -644,10 +636,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DAFB7A-0EF0-4F72-9492-60109C43E0EF}">
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>6</v>
       </c>
@@ -704,8 +696,11 @@
         <f>N1+2</f>
         <v>46150</v>
       </c>
+      <c r="P1" s="17">
+        <v>46153</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
@@ -751,8 +746,11 @@
       <c r="O2" s="5">
         <v>16.399999999999999</v>
       </c>
+      <c r="P2" s="18">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -798,8 +796,11 @@
       <c r="O3" s="5">
         <v>17.7</v>
       </c>
+      <c r="P3" s="18">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -845,8 +846,11 @@
       <c r="O4" s="5">
         <v>16.2</v>
       </c>
+      <c r="P4" s="18">
+        <v>16.399999999999999</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -892,8 +896,11 @@
       <c r="O5" s="5">
         <v>15.4</v>
       </c>
+      <c r="P5" s="19">
+        <v>16.2</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -939,8 +946,11 @@
       <c r="O6" s="1">
         <v>16.100000000000001</v>
       </c>
+      <c r="P6">
+        <v>16.3</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>1</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="O7" s="9">
         <v>18.3</v>
       </c>
+      <c r="P7" s="19">
+        <v>17.600000000000001</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>1</v>
       </c>
@@ -1033,8 +1046,11 @@
       <c r="O8" s="5">
         <v>17.2</v>
       </c>
+      <c r="P8" s="19">
+        <v>16.8</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>1</v>
       </c>
@@ -1080,8 +1096,11 @@
       <c r="O9" s="5">
         <v>17.399999999999999</v>
       </c>
+      <c r="P9" s="19">
+        <v>18.2</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
@@ -1127,8 +1146,11 @@
       <c r="O10" s="5">
         <v>18.100000000000001</v>
       </c>
+      <c r="P10" s="19">
+        <v>17.399999999999999</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>1</v>
       </c>
@@ -1173,6 +1195,9 @@
       </c>
       <c r="O11" s="1">
         <v>17.2</v>
+      </c>
+      <c r="P11" s="19">
+        <v>17.399999999999999</v>
       </c>
     </row>
   </sheetData>
